--- a/elite-data/manifest-templates/EL_template_AssayBsSeqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayBsSeqTemplate.xlsx
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="138">
   <si>
     <t>Filename</t>
   </si>
@@ -427,7 +427,7 @@
     <t>l</t>
   </si>
   <si>
-    <t>sac-seq</t>
+    <t>Qiagen Rneasy Extraction Kit</t>
   </si>
   <si>
     <t>M</t>
@@ -436,7 +436,7 @@
     <t>PCRfree</t>
   </si>
   <si>
-    <t>Smart-seq1</t>
+    <t>sac-seq</t>
   </si>
   <si>
     <t>mg</t>
@@ -445,7 +445,7 @@
     <t>polyAselection</t>
   </si>
   <si>
-    <t>Smart-seq2</t>
+    <t>Smart-seq1</t>
   </si>
   <si>
     <t>mg/dl</t>
@@ -454,7 +454,7 @@
     <t>proximity ligation</t>
   </si>
   <si>
-    <t>Smart-seq4</t>
+    <t>Smart-seq2</t>
   </si>
   <si>
     <t>mg/l</t>
@@ -463,7 +463,7 @@
     <t>rRNAdepletion</t>
   </si>
   <si>
-    <t>SMRTbell</t>
+    <t>Smart-seq4</t>
   </si>
   <si>
     <t>mg/ml</t>
@@ -472,7 +472,7 @@
     <t>snIsoSeq</t>
   </si>
   <si>
-    <t>TruSeq</t>
+    <t>SMRTbell</t>
   </si>
   <si>
     <t>miu/ml</t>
@@ -481,13 +481,16 @@
     <t>SPLITseq</t>
   </si>
   <si>
-    <t>Ultralow Methyl-Seq</t>
+    <t>TruSeq</t>
   </si>
   <si>
     <t>ml</t>
   </si>
   <si>
     <t>STARRSeq</t>
+  </si>
+  <si>
+    <t>Ultralow Methyl-Seq</t>
   </si>
   <si>
     <t>mM</t>
@@ -35014,11 +35017,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="R2:R1000">
       <formula1>Sheet2!$R$2:$R$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="M2:M1000">
-      <formula1>Sheet2!$M$2:$M$22</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
       <formula1>Sheet2!$V$2:$V$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="M2:M1000">
+      <formula1>Sheet2!$M$2:$M$23</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -35428,28 +35431,31 @@
         <v>101</v>
       </c>
       <c r="M22" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="J23" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M23" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23">
-      <c r="J23" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
     <row r="24">
       <c r="J24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
       <c r="J25" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>62</v>
@@ -35457,32 +35463,32 @@
     </row>
     <row r="26">
       <c r="J26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27">
       <c r="J27" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28">
       <c r="J28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29">
       <c r="J29" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
       <c r="J30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31">
       <c r="J31" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32">
@@ -35502,122 +35508,122 @@
     </row>
     <row r="35">
       <c r="J35" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36">
       <c r="J36" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37">
       <c r="J37" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38">
       <c r="J38" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39">
       <c r="J39" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40">
       <c r="J40" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41">
       <c r="J41" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42">
       <c r="J42" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43">
       <c r="J43" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44">
       <c r="J44" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45">
       <c r="J45" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46">
       <c r="J46" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47">
       <c r="J47" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48">
       <c r="J48" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49">
       <c r="J49" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50">
       <c r="J50" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51">
       <c r="J51" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52">
       <c r="J52" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53">
       <c r="J53" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="J54" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="J55" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56">
       <c r="J56" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57">
       <c r="J57" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58">
       <c r="J58" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59">

--- a/elite-data/manifest-templates/EL_template_AssayBsSeqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayBsSeqTemplate.xlsx
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="137">
   <si>
     <t>Filename</t>
   </si>
@@ -365,9 +365,6 @@
   </si>
   <si>
     <t>stranded</t>
-  </si>
-  <si>
-    <t>singleEnd pairedEnd</t>
   </si>
   <si>
     <t>Unknown</t>
@@ -35009,6 +35006,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="J2:J1000">
       <formula1>Sheet2!$J$2:$J$59</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
+      <formula1>Sheet2!$V$2:$V$7</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="L2:L1000">
       <formula1>Sheet2!$L$2:$L$25</formula1>
     </dataValidation>
@@ -35020,9 +35020,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="R2:R1000">
       <formula1>Sheet2!$R$2:$R$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
-      <formula1>Sheet2!$V$2:$V$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="M2:M1000">
       <formula1>Sheet2!$M$2:$M$23</formula1>
@@ -35261,46 +35258,43 @@
         <v>61</v>
       </c>
       <c r="X7" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="J8" s="6" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="J8" s="6" t="s">
+      <c r="L8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="M8" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="S8" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="J9" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="S8" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="J9" s="6" t="s">
+      <c r="L9" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="M9" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="S9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="S9" s="6" t="s">
+    </row>
+    <row r="10">
+      <c r="J10" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="J10" s="6" t="s">
+      <c r="L10" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>38</v>
@@ -35308,10 +35302,10 @@
     </row>
     <row r="11">
       <c r="J11" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>43</v>
@@ -35319,10 +35313,10 @@
     </row>
     <row r="12">
       <c r="J12" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>47</v>
@@ -35330,169 +35324,169 @@
     </row>
     <row r="13">
       <c r="J13" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>38</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="J14" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>43</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="J15" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="J16" s="6" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="J16" s="6" t="s">
+      <c r="L16" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="M16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="M16" s="6" t="s">
+    </row>
+    <row r="17">
+      <c r="J17" s="6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="J17" s="6" t="s">
+      <c r="L17" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="M17" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="M17" s="6" t="s">
+    </row>
+    <row r="18">
+      <c r="J18" s="6" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="J18" s="6" t="s">
+      <c r="L18" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="M18" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="M18" s="6" t="s">
+    </row>
+    <row r="19">
+      <c r="J19" s="6" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="J19" s="6" t="s">
+      <c r="L19" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="M19" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="M19" s="6" t="s">
+    </row>
+    <row r="20">
+      <c r="J20" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="J20" s="6" t="s">
+      <c r="L20" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="L20" s="6" t="s">
+      <c r="M20" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="M20" s="6" t="s">
+    </row>
+    <row r="21">
+      <c r="J21" s="6" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="J21" s="6" t="s">
+      <c r="L21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="M21" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="M21" s="6" t="s">
+    </row>
+    <row r="22">
+      <c r="J22" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="J22" s="6" t="s">
+      <c r="L22" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="M22" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="M22" s="6" t="s">
+    </row>
+    <row r="23">
+      <c r="J23" s="6" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="J23" s="6" t="s">
+      <c r="L23" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="M23" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="J24" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="M23" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="J24" s="6" t="s">
+      <c r="L24" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L24" s="6" t="s">
+    </row>
+    <row r="25">
+      <c r="J25" s="6" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="J25" s="6" t="s">
+      <c r="L25" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="J26" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="L25" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="J26" s="6" t="s">
+    </row>
+    <row r="27">
+      <c r="J27" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="27">
-      <c r="J27" s="6" t="s">
+    <row r="28">
+      <c r="J28" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="28">
-      <c r="J28" s="6" t="s">
+    <row r="29">
+      <c r="J29" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="29">
-      <c r="J29" s="6" t="s">
+    <row r="30">
+      <c r="J30" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30">
-      <c r="J30" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
     <row r="31">
       <c r="J31" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32">
@@ -35512,127 +35506,127 @@
     </row>
     <row r="35">
       <c r="J35" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="J36" s="6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="36">
-      <c r="J36" s="6" t="s">
+    <row r="37">
+      <c r="J37" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="37">
-      <c r="J37" s="6" t="s">
+    <row r="38">
+      <c r="J38" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="38">
-      <c r="J38" s="6" t="s">
+    <row r="39">
+      <c r="J39" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="39">
-      <c r="J39" s="6" t="s">
+    <row r="40">
+      <c r="J40" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="40">
-      <c r="J40" s="6" t="s">
+    <row r="41">
+      <c r="J41" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="41">
-      <c r="J41" s="6" t="s">
+    <row r="42">
+      <c r="J42" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42">
-      <c r="J42" s="6" t="s">
+    <row r="43">
+      <c r="J43" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="43">
-      <c r="J43" s="6" t="s">
+    <row r="44">
+      <c r="J44" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="44">
-      <c r="J44" s="6" t="s">
+    <row r="45">
+      <c r="J45" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="45">
-      <c r="J45" s="6" t="s">
+    <row r="46">
+      <c r="J46" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="46">
-      <c r="J46" s="6" t="s">
+    <row r="47">
+      <c r="J47" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="47">
-      <c r="J47" s="6" t="s">
+    <row r="48">
+      <c r="J48" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="48">
-      <c r="J48" s="6" t="s">
+    <row r="49">
+      <c r="J49" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="49">
-      <c r="J49" s="6" t="s">
+    <row r="50">
+      <c r="J50" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="50">
-      <c r="J50" s="6" t="s">
+    <row r="51">
+      <c r="J51" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="51">
-      <c r="J51" s="6" t="s">
+    <row r="52">
+      <c r="J52" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="52">
-      <c r="J52" s="6" t="s">
+    <row r="53">
+      <c r="J53" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="53">
-      <c r="J53" s="6" t="s">
+    <row r="54">
+      <c r="J54" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="54">
-      <c r="J54" s="6" t="s">
+    <row r="55">
+      <c r="J55" s="6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="55">
-      <c r="J55" s="6" t="s">
+    <row r="56">
+      <c r="J56" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="56">
-      <c r="J56" s="6" t="s">
+    <row r="57">
+      <c r="J57" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="57">
-      <c r="J57" s="6" t="s">
+    <row r="58">
+      <c r="J58" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="58">
-      <c r="J58" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
     <row r="59">
       <c r="J59" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/elite-data/manifest-templates/EL_template_AssayBsSeqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayBsSeqTemplate.xlsx
@@ -298,7 +298,7 @@
     <t>forward</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>AI</t>
@@ -313,7 +313,7 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>AU/ml</t>
@@ -367,7 +367,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>gm</t>
